--- a/docs/reports/ممیزی-محصولات-دور۲-2026-08-31.xlsx
+++ b/docs/reports/ممیزی-محصولات-دور۲-2026-08-31.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,8 +85,20 @@
       <name val="Arial"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +123,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EAF1F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -140,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -184,6 +201,13 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -683,6 +707,20 @@
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">        اگر تعلیق زدید، فعلاً موجودی‌اش صفر می‌شود تا به‌عنوان ناموجود دیده شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>به‌روزرسانیِ ۳۱ اوت: نشانیِ صفحاتِ محصول در سایت عوض شده و لینک‌هایِ این فایل با نشانیِ جدید به‌روز شده‌اند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>به‌روزرسانیِ ۳۱ اوت: نشانیِ صفحاتِ محصول در سایت عوض شد؛ لینک‌هایِ این فایل با نشانیِ جدید به‌روز شدند و نامِ چند محصول هم با نامِ فعلیِ سایت هم‌راست شد.</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1344,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>آنتن دیش نیر SP62-30 XD — ۳۰dBi دوقطبی</t>
+          <t>آنتن دیش وایمکس‌نیر SP62-30 XD — ۳۰dBi دوقطبی</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1346,7 +1384,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">آنتن دیش نیر SP62-30D — ۳۰dBi باند ۵ گیگاهرتز </t>
+          <t>آنتن دیش وایمکس‌نیر SP62-30D — ۳۰dBi دوقطبی</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1386,7 +1424,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>آنتن دیش نیر SP62-33 LO — ۳۳dBi دوقطبی</t>
+          <t>آنتن دیش وایمکس‌نیر SP62-33 LO — ۳۳dBi دوقطبی</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1426,7 +1464,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>آنتن دیش نیر ۲۷dBi باند ۵ گیگاهرتز</t>
+          <t>آنتن دیش وایمکس‌نیر ۲۷dBi دوقطبی</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1466,7 +1504,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>آنتن دیش نیر ۳۰dBi باند ۵ گیگاهرتز</t>
+          <t>آنتن دیش وایمکس‌نیر ۳۰dBi دوقطبی</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -1506,7 +1544,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>آنتن دیش نیر ۳۰dBi دوقطبی — نسخهٔ L</t>
+          <t>آنتن دیش وایمکس‌نیر ۳۰dBi دوقطبی — نسخهٔ L</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1546,7 +1584,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>آنتن دیش نیر ۳۲dBi باند ۵ گیگاهرتز</t>
+          <t>آنتن دیش وایمکس‌نیر ۳۲dBi دوقطبی</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1586,7 +1624,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>آنتن دیش نیر ۳۲dBi دوقطبی HP — رادوم‌دار</t>
+          <t>آنتن دیش وایمکس‌نیر ۳۲dBi دوقطبی HP — رادوم‌دار</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1626,7 +1664,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>آنتن دیش نیر ۳۳dBi باند ۵ گیگاهرتز</t>
+          <t>آنتن دیش وایمکس‌نیر ۳۳dBi دوقطبی</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -5798,9 +5836,9 @@
           <t>رادیو وایرلس</t>
         </is>
       </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>باز کردن صفحهٔ محصول</t>
+      <c r="D132" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -5809,9 +5847,9 @@
       <c r="F132" s="7" t="n">
         <v>800000</v>
       </c>
-      <c r="G132" s="8" t="inlineStr">
-        <is>
-          <t>هنوز تعیین‌تکلیف نشده</t>
+      <c r="G132" s="18" t="inlineStr">
+        <is>
+          <t>⚠️ این محصول دیگر روی سایت نیست — هنگامِ انتقالِ دادهٔ جدید حذف شد و تصمیمی هم درباره‌اش ثبت نشده بود. اگر باید برگردد بگویید.</t>
         </is>
       </c>
       <c r="H132" s="9" t="inlineStr"/>
@@ -8754,7 +8792,7 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>آنتن دیش نیر SP62-35D — ۳۵dBi باند ۵ گیگاهرتز</t>
+          <t>آنتن دیش وایمکس‌نیر SP62-35D — ۳۵dBi دوقطبی</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
@@ -9006,87 +9044,86 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D159" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D160" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D161" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D162" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D163" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D164" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D165" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D166" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D167" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D168" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D169" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D170" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D171" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D172" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D173" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D174" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D175" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D176" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D177" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D178" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D179" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D180" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D181" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D182" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D183" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D184" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D185" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D186" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D187" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D188" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D189" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D190" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D191" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D192" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D193" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D194" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D195" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D196" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D197" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D198" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D199" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D200" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D201" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D202" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D203" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D204" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D205" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D206" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D207" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D208" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D209" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D210" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D211" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D212" r:id="rId210"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
